--- a/data/trans_orig/P05A07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P05A07-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2012</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96486</t>
+          <t>97591</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129963</t>
+          <t>129916</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88984</t>
+          <t>89830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122613</t>
+          <t>122179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193614</t>
+          <t>198213</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>242800</t>
+          <t>245528</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90005</t>
+          <t>91380</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124109</t>
+          <t>124409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79979</t>
+          <t>80091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112992</t>
+          <t>114031</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179514</t>
+          <t>178685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227454</t>
+          <t>224881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56093</t>
+          <t>57185</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86301</t>
+          <t>87157</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>65833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>98095</t>
+          <t>98670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>131891</t>
+          <t>131920</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>175487</t>
+          <t>175898</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282303</t>
+          <t>282910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>329260</t>
+          <t>327909</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>298188</t>
+          <t>296865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>342002</t>
+          <t>343761</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>587728</t>
+          <t>591848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>655397</t>
+          <t>656611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>119274</t>
+          <t>122890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>163594</t>
+          <t>163821</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>122593</t>
+          <t>122773</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>163296</t>
+          <t>165050</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>256185</t>
+          <t>255261</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>315486</t>
+          <t>312529</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42847</t>
+          <t>42643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73770</t>
+          <t>72979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42990</t>
+          <t>42445</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71103</t>
+          <t>72085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92114</t>
+          <t>93686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134203</t>
+          <t>135889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103332</t>
+          <t>101418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137700</t>
+          <t>136103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113324</t>
+          <t>111721</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149120</t>
+          <t>148972</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>224101</t>
+          <t>225348</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>274800</t>
+          <t>275870</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143119</t>
+          <t>143019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178450</t>
+          <t>178196</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137527</t>
+          <t>136362</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175752</t>
+          <t>174219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>288098</t>
+          <t>286546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339085</t>
+          <t>339257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33759</t>
+          <t>32936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58371</t>
+          <t>57044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42323</t>
+          <t>44040</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>72087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82601</t>
+          <t>83249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120070</t>
+          <t>120742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>207865</t>
+          <t>207988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>247509</t>
+          <t>246862</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>213523</t>
+          <t>214905</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>252817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>435916</t>
+          <t>435925</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>488445</t>
+          <t>488775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,42%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74366</t>
+          <t>74158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108342</t>
+          <t>110170</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67983</t>
+          <t>68765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100659</t>
+          <t>102383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151117</t>
+          <t>152471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198428</t>
+          <t>198619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>40478</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68202</t>
+          <t>69610</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55020</t>
+          <t>52778</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85054</t>
+          <t>82690</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102300</t>
+          <t>102216</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143031</t>
+          <t>142891</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84720</t>
+          <t>83602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114716</t>
+          <t>114555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69734</t>
+          <t>70287</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100832</t>
+          <t>100517</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>163443</t>
+          <t>161430</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>205219</t>
+          <t>204351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66740</t>
+          <t>66273</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95327</t>
+          <t>96422</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81660</t>
+          <t>81666</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>111410</t>
+          <t>109744</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>152493</t>
+          <t>155894</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>195480</t>
+          <t>197417</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23363</t>
+          <t>22838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44616</t>
+          <t>44631</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28960</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51367</t>
+          <t>51943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59122</t>
+          <t>57664</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89325</t>
+          <t>89981</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85568</t>
+          <t>85785</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118094</t>
+          <t>118891</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101179</t>
+          <t>100881</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>133935</t>
+          <t>135958</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>192415</t>
+          <t>195852</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>243147</t>
+          <t>242271</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>124737</t>
+          <t>123210</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157901</t>
+          <t>158366</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>118346</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152964</t>
+          <t>152979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>253030</t>
+          <t>253632</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>302160</t>
+          <t>301153</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,36%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>21652</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44685</t>
+          <t>43869</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>17159</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38000</t>
+          <t>37708</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45389</t>
+          <t>45401</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76279</t>
+          <t>73714</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>256903</t>
+          <t>258818</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>310325</t>
+          <t>310332</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>255469</t>
+          <t>255122</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>306708</t>
+          <t>309077</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>523141</t>
+          <t>525152</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>599764</t>
+          <t>600588</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>266649</t>
+          <t>264053</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>318427</t>
+          <t>316690</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>280829</t>
+          <t>279278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>333689</t>
+          <t>334066</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>562747</t>
+          <t>565487</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>636495</t>
+          <t>638333</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,12%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71190</t>
+          <t>71123</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108852</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>86054</t>
+          <t>85053</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>127543</t>
+          <t>124861</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>163813</t>
+          <t>167268</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>220763</t>
+          <t>221530</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>522253</t>
+          <t>518695</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>577294</t>
+          <t>574475</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>535881</t>
+          <t>536681</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>594223</t>
+          <t>593586</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1075548</t>
+          <t>1073684</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1151779</t>
+          <t>1151785</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>151572</t>
+          <t>151028</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>202535</t>
+          <t>202980</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>175880</t>
+          <t>180600</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>228989</t>
+          <t>232416</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>347229</t>
+          <t>347403</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>418599</t>
+          <t>420504</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>40098</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>69412</t>
+          <t>68512</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>39275</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>68351</t>
+          <t>67736</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>86525</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>128045</t>
+          <t>126242</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1743116</t>
+          <t>1729135</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1858701</t>
+          <t>1849140</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1778080</t>
+          <t>1780728</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1901421</t>
+          <t>1899873</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3552114</t>
+          <t>3552897</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3721761</t>
+          <t>3722514</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1133805</t>
+          <t>1132119</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1245132</t>
+          <t>1247293</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1159305</t>
+          <t>1157912</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1278472</t>
+          <t>1273602</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2330850</t>
+          <t>2328104</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2489938</t>
+          <t>2487926</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>392611</t>
+          <t>394468</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>476508</t>
+          <t>472340</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>443808</t>
+          <t>447356</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>528677</t>
+          <t>530518</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>861559</t>
+          <t>862966</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>978613</t>
+          <t>976599</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2016</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2016 (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121651</t>
+          <t>122693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155612</t>
+          <t>157842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107005</t>
+          <t>107855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140300</t>
+          <t>140560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239547</t>
+          <t>242279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>288082</t>
+          <t>290249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84595</t>
+          <t>80261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119269</t>
+          <t>114289</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77356</t>
+          <t>78535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110567</t>
+          <t>108968</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167668</t>
+          <t>168312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214944</t>
+          <t>215350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37997</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65710</t>
+          <t>65267</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52522</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82903</t>
+          <t>81545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98488</t>
+          <t>99723</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>140234</t>
+          <t>139640</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>291576</t>
+          <t>292732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335662</t>
+          <t>336185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295502</t>
+          <t>296493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>342503</t>
+          <t>341526</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>602158</t>
+          <t>603193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>663974</t>
+          <t>668061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,33%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112648</t>
+          <t>113213</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>154674</t>
+          <t>151815</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>110319</t>
+          <t>111326</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>152243</t>
+          <t>153728</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>233586</t>
+          <t>236569</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>289770</t>
+          <t>294197</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>42050</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69692</t>
+          <t>70386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54272</t>
+          <t>55044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86690</t>
+          <t>88000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105951</t>
+          <t>105669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147897</t>
+          <t>148813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>197217</t>
+          <t>196028</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>229737</t>
+          <t>228735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222402</t>
+          <t>222090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>256310</t>
+          <t>256557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>429378</t>
+          <t>428512</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>475610</t>
+          <t>475334</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76322</t>
+          <t>78253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107245</t>
+          <t>109981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70980</t>
+          <t>69908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102186</t>
+          <t>103763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157248</t>
+          <t>155808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202429</t>
+          <t>202721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20310</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13956</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>32150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>244391</t>
+          <t>246095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>279224</t>
+          <t>282767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>250524</t>
+          <t>251041</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>287651</t>
+          <t>286312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>507382</t>
+          <t>508927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>557476</t>
+          <t>560130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48680</t>
+          <t>48022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78551</t>
+          <t>79448</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51508</t>
+          <t>52718</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83671</t>
+          <t>82484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108876</t>
+          <t>107851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150678</t>
+          <t>151774</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>27703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52657</t>
+          <t>52549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>37444</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65648</t>
+          <t>65367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71762</t>
+          <t>71227</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>107717</t>
+          <t>107060</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113364</t>
+          <t>112650</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>140878</t>
+          <t>140856</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136834</t>
+          <t>138010</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163646</t>
+          <t>164189</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>259495</t>
+          <t>259786</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>298752</t>
+          <t>300472</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53028</t>
+          <t>53184</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>79923</t>
+          <t>80452</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34083</t>
+          <t>33799</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57037</t>
+          <t>56562</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>93762</t>
+          <t>92510</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>129248</t>
+          <t>129938</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26166</t>
+          <t>27801</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,82 +7137,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>21993</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>14183</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>31968</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>39584</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>28547</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>53232</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>12,39%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>21993</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>14234</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>32917</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>39584</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>28994</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>52707</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>173823</t>
+          <t>173826</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>202888</t>
+          <t>202465</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>186132</t>
+          <t>185101</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>214456</t>
+          <t>215240</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>369795</t>
+          <t>369242</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>412124</t>
+          <t>410364</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65327</t>
+          <t>66762</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35018</t>
+          <t>36628</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61743</t>
+          <t>63501</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81059</t>
+          <t>84003</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>117869</t>
+          <t>121617</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>28435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14991</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34674</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55438</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>311433</t>
+          <t>315520</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>365394</t>
+          <t>370597</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>314179</t>
+          <t>310933</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>367388</t>
+          <t>366045</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>643070</t>
+          <t>640458</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>720388</t>
+          <t>714803</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>198802</t>
+          <t>194997</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>251703</t>
+          <t>248126</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,82 +7936,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>29,74%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>37,84%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>217171</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>194071</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>241778</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>28,25%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>35,19%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>440047</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>407094</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>476386</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>32,77%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>30,32%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>38,39%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>217171</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>194364</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>243635</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>35,46%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>440047</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>405738</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>477239</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>32,77%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>75017</t>
+          <t>74303</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111974</t>
+          <t>113031</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109388</t>
+          <t>108773</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>152495</t>
+          <t>151817</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>191203</t>
+          <t>195426</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>250790</t>
+          <t>253166</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>598916</t>
+          <t>595067</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>643940</t>
+          <t>641423</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>640981</t>
+          <t>638876</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>685633</t>
+          <t>685635</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1249938</t>
+          <t>1251784</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1311838</t>
+          <t>1314582</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>88441</t>
+          <t>91275</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>127303</t>
+          <t>129436</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>100109</t>
+          <t>99215</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>141314</t>
+          <t>139652</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>200929</t>
+          <t>200714</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>257985</t>
+          <t>257558</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>34761</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>62465</t>
+          <t>63065</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>28145</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>52821</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>71436</t>
+          <t>70626</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>107787</t>
+          <t>107123</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2151544</t>
+          <t>2159371</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2265633</t>
+          <t>2269493</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2249527</t>
+          <t>2252318</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2360649</t>
+          <t>2362044</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4437544</t>
+          <t>4441809</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4592643</t>
+          <t>4598625</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>783868</t>
+          <t>779793</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>884938</t>
+          <t>883661</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>759569</t>
+          <t>756270</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>856330</t>
+          <t>862783</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1573943</t>
+          <t>1569334</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1711338</t>
+          <t>1719785</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>303063</t>
+          <t>302388</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>372463</t>
+          <t>370654</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>371894</t>
+          <t>374471</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>453696</t>
+          <t>450897</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>689472</t>
+          <t>697281</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>799951</t>
+          <t>804012</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2023</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>277706</t>
+          <t>277707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>298386</t>
+          <t>297917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>270045</t>
+          <t>269724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281217</t>
+          <t>281335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>552307</t>
+          <t>552000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>577254</t>
+          <t>576878</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26381</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14620</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36955</t>
+          <t>35622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>21202</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399721</t>
+          <t>397579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441034</t>
+          <t>441546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394507</t>
+          <t>394364</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>428189</t>
+          <t>426484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>805215</t>
+          <t>804987</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859689</t>
+          <t>857609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>55916</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93550</t>
+          <t>94905</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>67144</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96790</t>
+          <t>96943</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>130410</t>
+          <t>133272</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>180243</t>
+          <t>180123</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37299</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>29801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32391</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62565</t>
+          <t>62267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>207831</t>
+          <t>208183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>239736</t>
+          <t>240634</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>255204</t>
+          <t>253439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>282007</t>
+          <t>280711</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>469923</t>
+          <t>469794</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>513199</t>
+          <t>512489</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>40947</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69126</t>
+          <t>68548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34946</t>
+          <t>34927</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55982</t>
+          <t>56243</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78610</t>
+          <t>81777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115924</t>
+          <t>115284</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49635</t>
+          <t>49228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26029</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44943</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59581</t>
+          <t>59440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88296</t>
+          <t>90474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>207157</t>
+          <t>206495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242627</t>
+          <t>243811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>334682</t>
+          <t>332860</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>408856</t>
+          <t>407740</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>554165</t>
+          <t>559168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>642516</t>
+          <t>643742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32655</t>
+          <t>31619</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59631</t>
+          <t>57807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37989</t>
+          <t>36840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84369</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78320</t>
+          <t>76144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129800</t>
+          <t>128293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59188</t>
+          <t>58518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26542</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63557</t>
+          <t>65084</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65166</t>
+          <t>64714</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>113238</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132280</t>
+          <t>134199</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150935</t>
+          <t>151826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>200593</t>
+          <t>200369</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236113</t>
+          <t>235535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341888</t>
+          <t>341417</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384564</t>
+          <t>381775</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22553</t>
+          <t>22205</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39675</t>
+          <t>38698</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>21213</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53585</t>
+          <t>53598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46522</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>84430</t>
+          <t>85960</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177640</t>
+          <t>177768</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204959</t>
+          <t>204684</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>177476</t>
+          <t>178452</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>199698</t>
+          <t>200969</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>363366</t>
+          <t>363741</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>397610</t>
+          <t>398317</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37360</t>
+          <t>37157</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59620</t>
+          <t>59485</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22791</t>
+          <t>22923</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39243</t>
+          <t>39168</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65202</t>
+          <t>64199</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92438</t>
+          <t>92819</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21247</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>40713</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29395</t>
+          <t>29953</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47619</t>
+          <t>47602</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>55370</t>
+          <t>55312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>81895</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>344762</t>
+          <t>345391</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>407441</t>
+          <t>404397</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>484357</t>
+          <t>484667</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>727555</t>
+          <t>710334</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>856109</t>
+          <t>853418</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1147257</t>
+          <t>1143676</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>119865</t>
+          <t>117494</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>171771</t>
+          <t>168324</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59840</t>
+          <t>68165</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>187700</t>
+          <t>187301</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>172193</t>
+          <t>180550</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>333915</t>
+          <t>338127</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>88081</t>
+          <t>86553</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>134536</t>
+          <t>131911</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54948</t>
+          <t>66013</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>183457</t>
+          <t>184306</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>150915</t>
+          <t>153583</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>289771</t>
+          <t>295713</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>668179</t>
+          <t>664477</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>845940</t>
+          <t>840151</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>487281</t>
+          <t>484661</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>531888</t>
+          <t>529962</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1172599</t>
+          <t>1172083</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1402055</t>
+          <t>1400981</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>66626</t>
+          <t>67894</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>203397</t>
+          <t>203278</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>130632</t>
+          <t>129799</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>168933</t>
+          <t>167991</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>182598</t>
+          <t>183169</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>353402</t>
+          <t>356057</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>62554</t>
+          <t>64181</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>47143</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>72943</t>
+          <t>73529</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>60001</t>
+          <t>59456</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>126322</t>
+          <t>126541</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2530324</t>
+          <t>2525983</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2834062</t>
+          <t>2794662</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2735857</t>
+          <t>2738428</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2982235</t>
+          <t>2968838</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5299365</t>
+          <t>5297229</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5651024</t>
+          <t>5674132</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,16%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>425937</t>
+          <t>434912</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>608139</t>
+          <t>616424</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,47 +13188,47 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>12,58%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>17,83%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>551521</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>457222</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>608826</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>12,32%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>551521</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>451294</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>609064</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>962630</t>
+          <t>945318</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1195153</t>
+          <t>1198308</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>228693</t>
+          <t>225212</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>340665</t>
+          <t>337701</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>275689</t>
+          <t>278067</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>383117</t>
+          <t>381928</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>552304</t>
+          <t>550355</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>705616</t>
+          <t>698791</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P05A07-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97591</t>
+          <t>96394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129916</t>
+          <t>129402</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122179</t>
+          <t>124660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198213</t>
+          <t>193208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>245528</t>
+          <t>243744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91380</t>
+          <t>91401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124409</t>
+          <t>122903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>31,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>95839</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>78865</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>111979</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>33,82%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>27,83%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>39,52%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>202892</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>180198</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>227150</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>35,3%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>31,35%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>95839</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>80091</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>114031</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>33,82%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>28,26%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>202892</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>178685</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>224881</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>31,09%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57185</t>
+          <t>56434</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87157</t>
+          <t>86188</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65833</t>
+          <t>66894</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>98670</t>
+          <t>99988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>131920</t>
+          <t>132040</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>175898</t>
+          <t>175281</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282910</t>
+          <t>284523</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327909</t>
+          <t>328699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296865</t>
+          <t>296903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>343761</t>
+          <t>343068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>591848</t>
+          <t>592262</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>656611</t>
+          <t>656751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,25%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122890</t>
+          <t>122309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>163821</t>
+          <t>163545</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>122773</t>
+          <t>121791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>165050</t>
+          <t>164072</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>255261</t>
+          <t>254055</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>312529</t>
+          <t>313542</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42643</t>
+          <t>42015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72979</t>
+          <t>74580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>41740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72085</t>
+          <t>70705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93686</t>
+          <t>93306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135889</t>
+          <t>138024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101418</t>
+          <t>102820</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>136103</t>
+          <t>135987</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111721</t>
+          <t>113510</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148972</t>
+          <t>151078</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275870</t>
+          <t>276812</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143019</t>
+          <t>142991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178196</t>
+          <t>178483</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136362</t>
+          <t>133257</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>174219</t>
+          <t>172251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>286546</t>
+          <t>288339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339257</t>
+          <t>339234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32936</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>57463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44040</t>
+          <t>43682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72087</t>
+          <t>71590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83249</t>
+          <t>81723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120742</t>
+          <t>120213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>207988</t>
+          <t>210356</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>246862</t>
+          <t>248501</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>214905</t>
+          <t>214941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252817</t>
+          <t>251434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>435925</t>
+          <t>434443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>488775</t>
+          <t>490553</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,65%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74158</t>
+          <t>75107</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110170</t>
+          <t>108100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68765</t>
+          <t>67533</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102383</t>
+          <t>100229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152471</t>
+          <t>152971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198619</t>
+          <t>199578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40478</t>
+          <t>40847</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69610</t>
+          <t>68557</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52778</t>
+          <t>54106</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>82753</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102216</t>
+          <t>99982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142891</t>
+          <t>143180</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83602</t>
+          <t>84462</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114555</t>
+          <t>115477</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70287</t>
+          <t>70823</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100517</t>
+          <t>100125</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>161430</t>
+          <t>162328</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>204351</t>
+          <t>204770</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>66416</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96422</t>
+          <t>96076</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81666</t>
+          <t>80682</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>109744</t>
+          <t>110310</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>155894</t>
+          <t>156050</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>197417</t>
+          <t>196661</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44631</t>
+          <t>45383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29117</t>
+          <t>29216</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51943</t>
+          <t>50709</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57664</t>
+          <t>58742</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89981</t>
+          <t>92970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85785</t>
+          <t>84811</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118891</t>
+          <t>117502</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100881</t>
+          <t>102040</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>135958</t>
+          <t>134666</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>195852</t>
+          <t>196634</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>242271</t>
+          <t>242879</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>123210</t>
+          <t>122754</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>158366</t>
+          <t>156259</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118346</t>
+          <t>119430</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152979</t>
+          <t>151982</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>253632</t>
+          <t>252094</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>301153</t>
+          <t>300588</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21652</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43869</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>37088</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45401</t>
+          <t>44484</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73714</t>
+          <t>74792</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>258818</t>
+          <t>255521</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>310332</t>
+          <t>309553</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>255122</t>
+          <t>255647</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>309077</t>
+          <t>310662</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>525152</t>
+          <t>523685</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>600588</t>
+          <t>598311</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>264053</t>
+          <t>267031</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>316690</t>
+          <t>319487</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>279278</t>
+          <t>279239</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>334066</t>
+          <t>333692</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>565487</t>
+          <t>562519</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>638333</t>
+          <t>635600</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71123</t>
+          <t>71016</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105910</t>
+          <t>108739</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>85053</t>
+          <t>85124</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>124861</t>
+          <t>126320</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>167268</t>
+          <t>166609</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>221530</t>
+          <t>221646</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>518695</t>
+          <t>520170</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>574475</t>
+          <t>571594</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>536681</t>
+          <t>540154</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>593586</t>
+          <t>591603</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1073684</t>
+          <t>1074425</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1151785</t>
+          <t>1152072</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>151028</t>
+          <t>154907</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>202980</t>
+          <t>203457</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>180600</t>
+          <t>179282</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>232416</t>
+          <t>228966</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>347403</t>
+          <t>344706</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>420504</t>
+          <t>417716</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>40063</t>
+          <t>40246</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>68512</t>
+          <t>69691</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>67736</t>
+          <t>67322</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>86525</t>
+          <t>86964</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>126242</t>
+          <t>127127</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1729135</t>
+          <t>1738050</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1849140</t>
+          <t>1854928</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1780728</t>
+          <t>1772456</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1899873</t>
+          <t>1896145</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3552897</t>
+          <t>3548327</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3722514</t>
+          <t>3729371</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1132119</t>
+          <t>1137479</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1247293</t>
+          <t>1249172</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1157912</t>
+          <t>1165054</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1273602</t>
+          <t>1284296</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2328104</t>
+          <t>2326407</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2487926</t>
+          <t>2489037</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>394468</t>
+          <t>395748</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>472340</t>
+          <t>473596</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>447356</t>
+          <t>442789</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>530518</t>
+          <t>529264</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>862966</t>
+          <t>856591</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>976599</t>
+          <t>976967</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122693</t>
+          <t>122485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>157842</t>
+          <t>159125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107855</t>
+          <t>107507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140560</t>
+          <t>141312</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242279</t>
+          <t>239862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>290249</t>
+          <t>290033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80261</t>
+          <t>82277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114289</t>
+          <t>116535</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78535</t>
+          <t>76737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108968</t>
+          <t>108959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168312</t>
+          <t>167969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215350</t>
+          <t>214839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38125</t>
+          <t>37782</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65267</t>
+          <t>64690</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53802</t>
+          <t>54307</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81545</t>
+          <t>84170</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>99723</t>
+          <t>98904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>139640</t>
+          <t>139097</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>292732</t>
+          <t>290539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>336185</t>
+          <t>334458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296493</t>
+          <t>294564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341526</t>
+          <t>342722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>603193</t>
+          <t>600723</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>668061</t>
+          <t>665782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,1%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113213</t>
+          <t>113620</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151815</t>
+          <t>151861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>111326</t>
+          <t>112298</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153728</t>
+          <t>154566</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>236569</t>
+          <t>234043</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>294197</t>
+          <t>292867</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42050</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70386</t>
+          <t>71553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55044</t>
+          <t>55558</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88000</t>
+          <t>89634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105669</t>
+          <t>105334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148813</t>
+          <t>149382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>196028</t>
+          <t>196634</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>228735</t>
+          <t>230347</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222090</t>
+          <t>221403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>256557</t>
+          <t>254341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>428512</t>
+          <t>429361</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>475334</t>
+          <t>476658</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,89%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78253</t>
+          <t>76945</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109981</t>
+          <t>108855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69908</t>
+          <t>71442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103763</t>
+          <t>105372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155808</t>
+          <t>156777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202721</t>
+          <t>203190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32150</t>
+          <t>32111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>246095</t>
+          <t>244228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>282767</t>
+          <t>278711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251041</t>
+          <t>249292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>286312</t>
+          <t>287250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>508927</t>
+          <t>507127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>560130</t>
+          <t>556431</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48022</t>
+          <t>49433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79448</t>
+          <t>79606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52718</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82484</t>
+          <t>82173</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107851</t>
+          <t>108977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151774</t>
+          <t>151416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>28605</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52549</t>
+          <t>52700</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37444</t>
+          <t>38686</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65367</t>
+          <t>65649</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71227</t>
+          <t>73295</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>107060</t>
+          <t>107494</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112650</t>
+          <t>113694</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>140856</t>
+          <t>141709</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138010</t>
+          <t>137549</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>164189</t>
+          <t>163371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>259786</t>
+          <t>259341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>300472</t>
+          <t>297924</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,32%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53184</t>
+          <t>52118</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80452</t>
+          <t>78821</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33799</t>
+          <t>35140</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56562</t>
+          <t>57147</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>92510</t>
+          <t>95278</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>129938</t>
+          <t>130579</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>14530</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31968</t>
+          <t>32738</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>29837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53232</t>
+          <t>53599</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>173826</t>
+          <t>174738</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>202465</t>
+          <t>203640</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>185101</t>
+          <t>185577</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>215240</t>
+          <t>214657</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>369242</t>
+          <t>368358</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>410364</t>
+          <t>410530</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40231</t>
+          <t>38736</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66762</t>
+          <t>65367</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36628</t>
+          <t>36834</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63501</t>
+          <t>63364</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84003</t>
+          <t>80679</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121617</t>
+          <t>118203</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28435</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>33305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30609</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>56118</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>315520</t>
+          <t>314044</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>370597</t>
+          <t>368120</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>310933</t>
+          <t>316007</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>366045</t>
+          <t>367280</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>640458</t>
+          <t>642780</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>714803</t>
+          <t>716869</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>194997</t>
+          <t>196443</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>248126</t>
+          <t>249907</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>194071</t>
+          <t>193265</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>241778</t>
+          <t>241504</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>407094</t>
+          <t>408086</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>476386</t>
+          <t>478497</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74303</t>
+          <t>75813</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>113031</t>
+          <t>113893</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108773</t>
+          <t>110604</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151817</t>
+          <t>151669</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>195426</t>
+          <t>193417</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>253166</t>
+          <t>252786</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>595067</t>
+          <t>600505</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>641423</t>
+          <t>642646</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>638876</t>
+          <t>639426</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>685635</t>
+          <t>685568</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1251784</t>
+          <t>1251266</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1314582</t>
+          <t>1314744</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>91275</t>
+          <t>90045</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>129436</t>
+          <t>127289</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>99215</t>
+          <t>102058</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>139652</t>
+          <t>144402</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>200714</t>
+          <t>199756</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>257558</t>
+          <t>259586</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>63065</t>
+          <t>63401</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>27313</t>
+          <t>27106</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>52821</t>
+          <t>52451</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>70626</t>
+          <t>70078</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>107123</t>
+          <t>106304</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2159371</t>
+          <t>2147596</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2269493</t>
+          <t>2263126</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2252318</t>
+          <t>2251117</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2362044</t>
+          <t>2362695</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4441809</t>
+          <t>4436786</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4598625</t>
+          <t>4601005</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>779793</t>
+          <t>788597</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>883661</t>
+          <t>886888</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>756270</t>
+          <t>757766</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>862783</t>
+          <t>856451</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1569334</t>
+          <t>1567552</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1719785</t>
+          <t>1718443</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>302388</t>
+          <t>302935</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>370654</t>
+          <t>373656</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>374471</t>
+          <t>374366</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>450897</t>
+          <t>455926</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>697281</t>
+          <t>693249</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>804012</t>
+          <t>800437</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -9407,32 +9407,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>290061</t>
+          <t>295596</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>277707</t>
+          <t>286148</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>297917</t>
+          <t>303417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9442,32 +9442,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>276706</t>
+          <t>301991</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>269724</t>
+          <t>295263</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281335</t>
+          <t>306445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9477,32 +9477,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>566765</t>
+          <t>597588</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>552000</t>
+          <t>585783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>576878</t>
+          <t>607518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -9520,32 +9520,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>26583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9555,32 +9555,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9590,32 +9590,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24191</t>
+          <t>26468</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -9633,32 +9633,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9668,32 +9668,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9703,32 +9703,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21202</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -9746,17 +9746,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9816,17 +9816,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421268</t>
+          <t>427485</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397579</t>
+          <t>404529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441546</t>
+          <t>448186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9898,32 +9898,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>412582</t>
+          <t>436271</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394364</t>
+          <t>416077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>426484</t>
+          <t>453545</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9933,32 +9933,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>833851</t>
+          <t>863756</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>804987</t>
+          <t>832888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>857609</t>
+          <t>890769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -9976,32 +9976,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73923</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55916</t>
+          <t>60321</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94905</t>
+          <t>99705</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10011,32 +10011,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81026</t>
+          <t>87698</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67144</t>
+          <t>73074</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96943</t>
+          <t>107303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10046,32 +10046,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>154949</t>
+          <t>167059</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>133272</t>
+          <t>143576</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>180123</t>
+          <t>194622</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -10089,32 +10089,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23199</t>
+          <t>23800</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38330</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14743</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>30668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10159,32 +10159,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44559</t>
+          <t>46325</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>33581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62267</t>
+          <t>63935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -10202,17 +10202,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10237,17 +10237,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10272,17 +10272,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10319,32 +10319,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>223880</t>
+          <t>225430</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>208183</t>
+          <t>209962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>240634</t>
+          <t>239857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10354,32 +10354,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>269455</t>
+          <t>273774</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>253439</t>
+          <t>261405</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>280711</t>
+          <t>287693</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10389,32 +10389,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>493335</t>
+          <t>499204</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>469794</t>
+          <t>477845</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>512489</t>
+          <t>518996</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -10432,32 +10432,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53163</t>
+          <t>52283</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>39987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68548</t>
+          <t>67218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10467,32 +10467,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>45799</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34927</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56243</t>
+          <t>56340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10502,32 +10502,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>97343</t>
+          <t>98083</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81777</t>
+          <t>81927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115284</t>
+          <t>117233</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -10545,32 +10545,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>37449</t>
+          <t>36642</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>48342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10580,32 +10580,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35493</t>
+          <t>36807</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46580</t>
+          <t>46856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10615,32 +10615,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>72942</t>
+          <t>73449</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59440</t>
+          <t>60622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90474</t>
+          <t>89087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -10658,17 +10658,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>314492</t>
+          <t>314355</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>314492</t>
+          <t>314355</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>314492</t>
+          <t>314355</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10693,17 +10693,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10728,17 +10728,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>663620</t>
+          <t>670736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>663620</t>
+          <t>670736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>663620</t>
+          <t>670736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10775,32 +10775,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>226237</t>
+          <t>277696</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>206495</t>
+          <t>254890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>243811</t>
+          <t>296288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10810,32 +10810,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>365264</t>
+          <t>298936</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>332860</t>
+          <t>279834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>407740</t>
+          <t>315251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>591501</t>
+          <t>576632</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>559168</t>
+          <t>545391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>643742</t>
+          <t>600631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -10888,32 +10888,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42916</t>
+          <t>47907</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31619</t>
+          <t>34828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57807</t>
+          <t>65416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10923,32 +10923,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>63053</t>
+          <t>70895</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>58103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83039</t>
+          <t>86575</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10958,32 +10958,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>105968</t>
+          <t>118802</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76144</t>
+          <t>98602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>128293</t>
+          <t>142555</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -11001,32 +11001,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43405</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30540</t>
+          <t>35174</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58518</t>
+          <t>66366</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11036,32 +11036,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46789</t>
+          <t>51445</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28177</t>
+          <t>40816</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65084</t>
+          <t>67862</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11071,32 +11071,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>90193</t>
+          <t>98987</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64714</t>
+          <t>82255</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113238</t>
+          <t>121219</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -11114,17 +11114,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11149,17 +11149,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>475105</t>
+          <t>421276</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>475105</t>
+          <t>421276</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>475105</t>
+          <t>421276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11184,17 +11184,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>787662</t>
+          <t>794421</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>787662</t>
+          <t>794421</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>787662</t>
+          <t>794421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11231,32 +11231,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>143315</t>
+          <t>164379</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134199</t>
+          <t>152416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151826</t>
+          <t>173382</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11266,32 +11266,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>214806</t>
+          <t>181297</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>200369</t>
+          <t>170621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>235535</t>
+          <t>189154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11301,32 +11301,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>358122</t>
+          <t>345676</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341417</t>
+          <t>329996</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>381775</t>
+          <t>358445</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>82,48%</t>
         </is>
       </c>
     </row>
@@ -11344,32 +11344,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29846</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22205</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38698</t>
+          <t>43599</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11379,32 +11379,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39985</t>
+          <t>44323</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>36393</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53598</t>
+          <t>55366</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11414,32 +11414,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>69831</t>
+          <t>77236</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48006</t>
+          <t>65506</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>85960</t>
+          <t>91266</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -11457,32 +11457,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10983</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11492,32 +11492,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11527,32 +11527,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -11570,17 +11570,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11640,17 +11640,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11687,32 +11687,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>192232</t>
+          <t>194135</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177768</t>
+          <t>179210</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204684</t>
+          <t>205317</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11722,32 +11722,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>189854</t>
+          <t>193601</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>178452</t>
+          <t>181943</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>200969</t>
+          <t>204590</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11757,32 +11757,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>382086</t>
+          <t>387736</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>363741</t>
+          <t>369522</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>398317</t>
+          <t>403373</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -11800,32 +11800,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>47343</t>
+          <t>46556</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37157</t>
+          <t>37093</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59485</t>
+          <t>58697</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11835,32 +11835,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>29883</t>
+          <t>31131</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22923</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>40694</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11870,27 +11870,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>77226</t>
+          <t>77688</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64199</t>
+          <t>64928</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92819</t>
+          <t>94156</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -11913,32 +11913,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>30061</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>22047</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>40713</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11948,32 +11948,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>37319</t>
+          <t>39018</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>31246</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47602</t>
+          <t>48591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11983,32 +11983,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>67380</t>
+          <t>69033</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>55312</t>
+          <t>57591</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>81895</t>
+          <t>83003</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -12026,17 +12026,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12061,17 +12061,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12096,17 +12096,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12143,32 +12143,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>374173</t>
+          <t>424865</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>345391</t>
+          <t>389720</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>404397</t>
+          <t>452105</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12178,32 +12178,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>579544</t>
+          <t>453194</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>484667</t>
+          <t>429644</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>710334</t>
+          <t>481201</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12213,32 +12213,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>953718</t>
+          <t>878060</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>853418</t>
+          <t>838441</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1143676</t>
+          <t>920624</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -12256,32 +12256,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>142669</t>
+          <t>168200</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117494</t>
+          <t>143540</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>168324</t>
+          <t>197160</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12291,32 +12291,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>135942</t>
+          <t>160672</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>68165</t>
+          <t>140888</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>187301</t>
+          <t>182933</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12326,32 +12326,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>278611</t>
+          <t>328872</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>180550</t>
+          <t>294104</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>338127</t>
+          <t>362607</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -12369,32 +12369,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>107109</t>
+          <t>124327</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>86553</t>
+          <t>103545</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>131911</t>
+          <t>151218</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12404,32 +12404,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>132724</t>
+          <t>154333</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66013</t>
+          <t>133848</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>184306</t>
+          <t>178263</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12439,32 +12439,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>239833</t>
+          <t>278660</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>153583</t>
+          <t>246633</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>295713</t>
+          <t>312048</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -12482,17 +12482,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>623951</t>
+          <t>717391</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>623951</t>
+          <t>717391</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>623951</t>
+          <t>717391</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12517,17 +12517,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>848211</t>
+          <t>768199</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>848211</t>
+          <t>768199</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>848211</t>
+          <t>768199</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12552,17 +12552,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1472162</t>
+          <t>1485591</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1472162</t>
+          <t>1485591</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1472162</t>
+          <t>1485591</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12599,32 +12599,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>744249</t>
+          <t>579742</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>664477</t>
+          <t>551103</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>840151</t>
+          <t>606871</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12634,32 +12634,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>508320</t>
+          <t>584730</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>484661</t>
+          <t>558614</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>529962</t>
+          <t>607972</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12669,32 +12669,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1252569</t>
+          <t>1164472</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1172083</t>
+          <t>1130005</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1400981</t>
+          <t>1200567</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -12712,32 +12712,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>142538</t>
+          <t>168353</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>67894</t>
+          <t>144197</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>203278</t>
+          <t>193742</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12747,32 +12747,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>149040</t>
+          <t>171930</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>129799</t>
+          <t>151749</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>167991</t>
+          <t>194871</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12782,32 +12782,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>291578</t>
+          <t>340283</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>183169</t>
+          <t>308421</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>356057</t>
+          <t>374007</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -12825,32 +12825,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>41933</t>
+          <t>49977</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>37822</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>64181</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12860,32 +12860,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>59841</t>
+          <t>74079</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>47753</t>
+          <t>58851</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>73529</t>
+          <t>91733</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12895,32 +12895,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>101774</t>
+          <t>124056</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>59456</t>
+          <t>104280</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>126541</t>
+          <t>147829</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -12938,17 +12938,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12973,17 +12973,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717201</t>
+          <t>830739</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717201</t>
+          <t>830739</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717201</t>
+          <t>830739</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13008,17 +13008,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1645921</t>
+          <t>1628811</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1645921</t>
+          <t>1628811</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1645921</t>
+          <t>1628811</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13055,32 +13055,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2615415</t>
+          <t>2589330</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2525983</t>
+          <t>2536045</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2794662</t>
+          <t>2650710</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13090,32 +13090,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2816531</t>
+          <t>2723796</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2738428</t>
+          <t>2672448</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2968838</t>
+          <t>2773821</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13125,32 +13125,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>5431947</t>
+          <t>5313125</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5297229</t>
+          <t>5235967</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5674132</t>
+          <t>5390941</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -13168,32 +13168,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>548176</t>
+          <t>612957</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>434912</t>
+          <t>568661</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>616424</t>
+          <t>662512</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13203,32 +13203,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>551521</t>
+          <t>621533</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>457222</t>
+          <t>580140</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>608826</t>
+          <t>661974</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13238,32 +13238,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1099697</t>
+          <t>1234490</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>945318</t>
+          <t>1171461</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1198308</t>
+          <t>1293907</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -13281,32 +13281,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>294339</t>
+          <t>326541</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>225212</t>
+          <t>293368</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>337701</t>
+          <t>371754</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13316,32 +13316,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>342031</t>
+          <t>386490</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>278067</t>
+          <t>352469</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>381928</t>
+          <t>425390</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13351,32 +13351,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>636370</t>
+          <t>713031</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>550355</t>
+          <t>660668</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>698791</t>
+          <t>764531</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -13394,17 +13394,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3457930</t>
+          <t>3528828</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3457930</t>
+          <t>3528828</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3457930</t>
+          <t>3528828</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13429,17 +13429,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3710083</t>
+          <t>3731819</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3710083</t>
+          <t>3731819</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3710083</t>
+          <t>3731819</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13464,17 +13464,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7168014</t>
+          <t>7260646</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7168014</t>
+          <t>7260646</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7168014</t>
+          <t>7260646</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
